--- a/excel/Raspored_odvoza_Zona8_2026.xlsx
+++ b/excel/Raspored_odvoza_Zona8_2026.xlsx
@@ -1015,14 +1015,14 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>• Biootpad se na ovom području ne odvozi; GOS predlaže kućno kompostiranje (www.gos.hr/biootpad).</t>
+          <t>• Biootpad se na ovom području ne odvozi; preporučuje se kućno kompostiranje.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>• Spremnike iznijeti na javnu površinu najkasnije do 07:00. Info: 0800 200 214, info@gos.hr, www.gos.hr</t>
+          <t>• Spremnike iznijeti na javnu površinu najkasnije do 07:00.</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Izvor: GOS d.o.o., RASPORED_2026_Zona_8_v2.pdf. "x" = odvoz tog dana. Spremnike iznijeti do 07:00. Prošli datumi su posivljeni.</t>
+          <t>"x" = odvoz tog dana. Spremnike iznijeti do 07:00. Prošli datumi su posivljeni.</t>
         </is>
       </c>
     </row>
